--- a/sample-data/ai-cashflow-variants/01-tiem-banh-may-som/input/03_so_quy_ngan_hang.xlsx
+++ b/sample-data/ai-cashflow-variants/01-tiem-banh-may-som/input/03_so_quy_ngan_hang.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="Rfe2e06fd7fd84b87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sổ tổng hợp" sheetId="2" r:id="R5770223e110a423b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R071ec1bf68f94613"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sổ tổng hợp" sheetId="2" r:id="Rcf132229bf6e40e0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/sample-data/ai-cashflow-variants/01-tiem-banh-may-som/input/03_so_quy_ngan_hang.xlsx
+++ b/sample-data/ai-cashflow-variants/01-tiem-banh-may-som/input/03_so_quy_ngan_hang.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R071ec1bf68f94613"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sổ tổng hợp" sheetId="2" r:id="Rcf132229bf6e40e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R3ad0fbc1dcd44e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sổ tổng hợp" sheetId="2" r:id="Rf07a09d0b5884513"/>
   </x:sheets>
 </x:workbook>
 </file>
